--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\defend the castle\other\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\catastrophe-war\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C599377E-2755-4CCA-A542-F2103621F693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67764248-7987-46D5-ADE0-386EEE61E133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{986527ED-7849-4F0B-A69E-87DCB2412201}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>選択対象用</t>
     <rPh sb="0" eb="2">
@@ -118,115 +118,106 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>number
+(INT,
+UNSIGNED,
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・・・</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stage_clear
+(BOOLEAN,
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>merit_clear_0
+(BOOLEAN,
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>merit_clear_9
+(BOOLEAN,
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>編成用</t>
+    <rPh sb="0" eb="3">
+      <t>ヘンセイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>name
+(VARCHAR(20)
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>all_composition</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>id
-(TINYINT,
+(INT,
 AUTO_INCREMENT,
 NOT NULL,
 PRIMARY KEY)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>id
-(TINYINT,
-NOT NULL,
-PRIMARY KEY)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>select_code
-(TINYINT,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>number
+  </si>
+  <si>
+    <t>right_weapon_0
+(INT,
+NOT NULL)</t>
+  </si>
+  <si>
+    <t>center_core_0
 (INT,
 UNSIGNED,
 NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>all_composition</t>
-  </si>
-  <si>
-    <t>・・・</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>stage_clear
-(BOOLEAN,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>a</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>merit_clear_0
-(BOOLEAN,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>merit_clear_9
-(BOOLEAN,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>center_core_0
-(TINYINT,
+  </si>
+  <si>
+    <t>left_weapon_0
+(INT,
+NOT NULL)</t>
+  </si>
+  <si>
+    <t>right_weapon_7
+(INT,
+NOT NULL)</t>
+  </si>
+  <si>
+    <t>center_core_7
+(INT,
 UNSIGNED,
 NOT NULL)</t>
   </si>
   <si>
-    <t>left_weapon_0
-(TINYINT,
-NOT NULL)</t>
-  </si>
-  <si>
-    <t>right_weapon_7
-(TINYINT,
-NOT NULL)</t>
-  </si>
-  <si>
-    <t>center_core_7
-(TINYINT,
-UNSIGNED,
-NOT NULL)</t>
-  </si>
-  <si>
     <t>left_weapon_7
-(TINYINT,
-NOT NULL)</t>
-  </si>
-  <si>
-    <t>編成用</t>
-    <rPh sb="0" eb="3">
-      <t>ヘンセイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>right_weapon_0
-(TINYINT,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>name
-(VARCHAR(20)
-NOT NULL,)</t>
-    <phoneticPr fontId="1"/>
+(INT,
+NOT NULL)</t>
+  </si>
+  <si>
+    <t>select_code
+(INT,
+NOT NULL)</t>
   </si>
 </sst>
 </file>
@@ -619,41 +610,41 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="90" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
@@ -661,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1">
         <v>-1</v>
@@ -673,7 +664,7 @@
         <v>-1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1">
         <v>-1</v>
@@ -690,7 +681,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -702,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -719,7 +710,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -731,7 +722,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1">
         <v>3</v>
@@ -753,12 +744,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="90" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
@@ -795,13 +786,13 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
@@ -861,16 +852,16 @@
         <v>11</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.45">
@@ -884,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -901,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -918,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -936,10 +927,10 @@
     </row>
     <row r="30" spans="1:6" ht="90" x14ac:dyDescent="0.45">
       <c r="B30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
